--- a/compare_results_1_roots.xlsx
+++ b/compare_results_1_roots.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ville\OneDrive\Documents\CIC\Tesis\experimentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ville\OneDrive\Documents\CIC\Tesis\graficas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8F8799-4B12-4267-A2B2-F2F45BB80EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A068137-4073-4EF8-9FAE-01E3534C72EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{29209FFB-1D87-461F-B393-683DDBCDEF3F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="14" xr2:uid="{29209FFB-1D87-461F-B393-683DDBCDEF3F}"/>
   </bookViews>
   <sheets>
     <sheet name="compare_results_1_roots" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,11 @@
     <sheet name="gap1" sheetId="8" r:id="rId8"/>
     <sheet name="gap2" sheetId="9" r:id="rId9"/>
     <sheet name="gap3" sheetId="10" r:id="rId10"/>
+    <sheet name="fortimes" sheetId="12" r:id="rId11"/>
+    <sheet name="timegreedy" sheetId="11" r:id="rId12"/>
+    <sheet name="time1" sheetId="13" r:id="rId13"/>
+    <sheet name="time2" sheetId="14" r:id="rId14"/>
+    <sheet name="time3" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="263">
   <si>
     <t>experiment</t>
   </si>
@@ -1375,15 +1380,20 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -1432,7 +1442,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="69">
     <dxf>
       <font>
         <b val="0"/>
@@ -2144,7 +2154,723 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.000%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.000%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.000%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2159,13 +2885,7 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.000%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.000%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.000%"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2229,9 +2949,65 @@
     <tableColumn id="24" xr3:uid="{B2F546AA-2490-4A1C-B835-30EEA0993895}" name="solution_rollout k=3"/>
     <tableColumn id="25" xr3:uid="{CD44B255-CDD8-40B0-834B-EB713E143293}" name="time_taken k=3"/>
     <tableColumn id="26" xr3:uid="{791F2CE7-1D29-4F44-8DE3-CF96E90D0D82}" name="optimal_rollout k=3"/>
-    <tableColumn id="27" xr3:uid="{A8207F6F-AC8A-4D98-B1ED-D5FEDD4669BB}" name="diff greedy optimo" dataDxfId="32">
+    <tableColumn id="27" xr3:uid="{A8207F6F-AC8A-4D98-B1ED-D5FEDD4669BB}" name="diff greedy optimo" dataDxfId="64">
       <calculatedColumnFormula>Table1[[#This Row],[optimal_iqcp]]-Table1[[#This Row],[optimal_greedy]]</calculatedColumnFormula>
     </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C6717393-95BD-4868-9F5D-5498770AB83A}" name="Table10" displayName="Table10" ref="A1:E11" totalsRowShown="0" dataDxfId="21" tableBorderDxfId="27">
+  <autoFilter ref="A1:E11" xr:uid="{C6717393-95BD-4868-9F5D-5498770AB83A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{F9E1517F-27E6-4A3F-9751-33EC34D9AB78}" name="3" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{4A001623-E5B8-47D6-AD60-BD12AA1DE9F3}" name="4" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{1B0EDDA7-B400-4E02-8215-B84A322C18B4}" name="5" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{12496992-0D19-445C-8783-823C1032DEB6}" name="6" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{268DA5DF-FC42-4866-8B37-9EC878543E28}" name="7" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{516E6902-0720-4CF8-94EA-5D2D7EBAEDC7}" name="Table11" displayName="Table11" ref="A1:E11" totalsRowShown="0" dataDxfId="14" tableBorderDxfId="20">
+  <autoFilter ref="A1:E11" xr:uid="{516E6902-0720-4CF8-94EA-5D2D7EBAEDC7}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{AD4C788C-77D9-41AE-A19E-CCD4B3F3D2E3}" name="3" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{46C75EBF-C8B2-4C3E-AE18-2DCD9B5DC1C5}" name="4" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{28FF1019-D991-4F8A-9755-1CF5B8143E24}" name="5" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{C44ADA52-9ABD-4376-93E8-A5F006464E92}" name="6" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{89E6F7A1-D65F-45E1-88A6-69281447506F}" name="7" dataDxfId="15"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1ED71064-6D48-490B-B9F4-8716FF35147A}" name="Table12" displayName="Table12" ref="A1:E11" totalsRowShown="0" dataDxfId="7" tableBorderDxfId="13">
+  <autoFilter ref="A1:E11" xr:uid="{1ED71064-6D48-490B-B9F4-8716FF35147A}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{8EF44012-B760-40BE-9ED0-E27D7B2A31D0}" name="3" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{C52B78E7-D4BD-428D-9C6E-EE0BFE459CCD}" name="4" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{95C107DB-468F-4602-AA7E-C1E222B48865}" name="5" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{084D0008-31DD-4276-8E79-50182D37E7C6}" name="6" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{54135225-A4F4-4869-B75E-017441561F54}" name="7" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{F9604797-759B-4BF1-9DBE-6A9E309B2C2C}" name="Table13" displayName="Table13" ref="A1:E11" totalsRowShown="0" dataDxfId="0" tableBorderDxfId="6">
+  <autoFilter ref="A1:E11" xr:uid="{F9604797-759B-4BF1-9DBE-6A9E309B2C2C}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{49DC345D-77B3-4978-9A8D-8008B98D63C6}" name="3" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D2833A54-2D0F-43E8-8A84-75CCD3A56C8B}" name="4" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{22C226F8-8A75-4CCC-9A89-91C79E4BC42F}" name="5" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{2E420ECD-C79A-4B76-A6F5-D1062845E54A}" name="6" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{AFF18EE3-D81A-43E7-96D3-16E583F5E0B3}" name="7" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2245,28 +3021,28 @@
     <tableColumn id="2" xr3:uid="{C661E170-E629-4DB1-AF14-6F9CE4E9972B}" name="prom iqcp ">
       <calculatedColumnFormula>AVERAGEIF(Table1[grado],comparacion!A2,Table1[optimal_iqcp])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{B13FC58A-7458-460F-9A62-4354BBBC8247}" name="prom greedy " dataDxfId="40">
+    <tableColumn id="3" xr3:uid="{B13FC58A-7458-460F-9A62-4354BBBC8247}" name="prom greedy " dataDxfId="63">
       <calculatedColumnFormula>AVERAGEIF(Table1[grado],Table2[[#This Row],[grado ]],Table1[optimal_greedy])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5108688B-7A0C-4EEE-BE0E-B51258251195}" name="prom k 1 " dataDxfId="39">
+    <tableColumn id="4" xr3:uid="{5108688B-7A0C-4EEE-BE0E-B51258251195}" name="prom k 1 " dataDxfId="62">
       <calculatedColumnFormula>AVERAGEIF(Table1[grado],Table2[[#This Row],[grado ]],Table1[optimal_rollout k=1])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{73B496D6-321F-49EE-AE98-C57B30DB2A9C}" name="prom k2 " dataDxfId="38">
+    <tableColumn id="5" xr3:uid="{73B496D6-321F-49EE-AE98-C57B30DB2A9C}" name="prom k2 " dataDxfId="61">
       <calculatedColumnFormula>AVERAGEIF(Table1[grado],Table2[[#This Row],[grado ]],Table1[optimal_rollout k=2])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{C1D90CE6-020B-4EA2-9526-7F59548DFEA7}" name="prom k3" dataDxfId="37">
+    <tableColumn id="6" xr3:uid="{C1D90CE6-020B-4EA2-9526-7F59548DFEA7}" name="prom k3" dataDxfId="60">
       <calculatedColumnFormula>AVERAGEIF(Table1[grado],Table2[[#This Row],[grado ]],Table1[optimal_rollout k=3])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{DA4BE40C-22D7-4871-964C-A49EA6785E9C}" name="gap k1" dataDxfId="36">
+    <tableColumn id="7" xr3:uid="{DA4BE40C-22D7-4871-964C-A49EA6785E9C}" name="gap k1" dataDxfId="59">
       <calculatedColumnFormula>(Table2[[#This Row],[prom iqcp ]]-Table2[[#This Row],[prom k 1 ]])/Table2[[#This Row],[prom iqcp ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{8C39CEEA-0CCF-464E-828C-620C3E9ABBF2}" name="gap k2w" dataDxfId="35">
+    <tableColumn id="8" xr3:uid="{8C39CEEA-0CCF-464E-828C-620C3E9ABBF2}" name="gap k2w" dataDxfId="58">
       <calculatedColumnFormula>(Table2[[#This Row],[prom iqcp ]]-Table2[[#This Row],[prom k2 ]])/Table2[[#This Row],[prom iqcp ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{C044DF31-DD8A-4957-B7F2-39B880422336}" name="gap k3" dataDxfId="34">
+    <tableColumn id="9" xr3:uid="{C044DF31-DD8A-4957-B7F2-39B880422336}" name="gap k3" dataDxfId="57">
       <calculatedColumnFormula>(Table2[[#This Row],[prom iqcp ]]-Table2[[#This Row],[prom k3]])/Table2[[#This Row],[prom iqcp ]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{9B273C95-3B22-4995-9A9E-E7EC6435D016}" name="gap greedy" dataDxfId="33">
+    <tableColumn id="10" xr3:uid="{9B273C95-3B22-4995-9A9E-E7EC6435D016}" name="gap greedy" dataDxfId="56">
       <calculatedColumnFormula>(Table2[[#This Row],[prom iqcp ]]-Table2[[#This Row],[prom greedy ]])/Table2[[#This Row],[prom iqcp ]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2288,16 +3064,16 @@
     <tableColumn id="20" xr3:uid="{1BD32639-3CD2-4BBA-9526-9242C81EDCA3}" name="optimal_rollout k=1"/>
     <tableColumn id="23" xr3:uid="{EFDE6CC9-CD9E-4007-9950-33D452DABC02}" name="optimal_rollout k=2"/>
     <tableColumn id="26" xr3:uid="{24023906-42CC-4AAA-942F-D91D2CCEDAF7}" name="optimal_rollout k=3"/>
-    <tableColumn id="2" xr3:uid="{4E41A7CA-B2A0-4F46-9F44-002F6EA4CFBA}" name="gap_greedy" dataDxfId="31">
+    <tableColumn id="2" xr3:uid="{4E41A7CA-B2A0-4F46-9F44-002F6EA4CFBA}" name="gap_greedy" dataDxfId="68">
       <calculatedColumnFormula>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_greedy]])/Table14[[#This Row],[optimal_iqcp]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{936EB1FD-BD4A-409D-937A-51012FA51107}" name="gap_1" dataDxfId="30">
+    <tableColumn id="3" xr3:uid="{936EB1FD-BD4A-409D-937A-51012FA51107}" name="gap_1" dataDxfId="67">
       <calculatedColumnFormula>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=1]])/Table14[[#This Row],[optimal_iqcp]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7C554CD3-BE49-4AC1-AEB8-2CA7421D28AA}" name="gap_2" dataDxfId="29">
+    <tableColumn id="4" xr3:uid="{7C554CD3-BE49-4AC1-AEB8-2CA7421D28AA}" name="gap_2" dataDxfId="66">
       <calculatedColumnFormula>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{8BD57CD0-30CB-4310-8F65-A6971F830CE2}" name="gap_3" dataDxfId="28">
+    <tableColumn id="5" xr3:uid="{8BD57CD0-30CB-4310-8F65-A6971F830CE2}" name="gap_3" dataDxfId="65">
       <calculatedColumnFormula>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2324,56 +3100,74 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E6D82BBE-DA87-4388-AF4E-854E634E6DC8}" name="Table5" displayName="Table5" ref="A1:E11" totalsRowShown="0" dataDxfId="21" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E6D82BBE-DA87-4388-AF4E-854E634E6DC8}" name="Table5" displayName="Table5" ref="A1:E11" totalsRowShown="0" dataDxfId="55" tableBorderDxfId="54">
   <autoFilter ref="A1:E11" xr:uid="{E6D82BBE-DA87-4388-AF4E-854E634E6DC8}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{B2153A76-F364-497F-ACF0-93130DEB56E5}" name="3" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{02EDDD9E-7839-4A7F-A198-B7C3BD4FE96D}" name="4" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{56C5BB89-7633-470D-BB51-9ACE7B10F91E}" name="5" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{CA94D498-A6BE-4017-9DCC-7DF63637F600}" name="6" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{BAD28F7F-2304-4D9A-A96E-925E4D7A8720}" name="7" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{B2153A76-F364-497F-ACF0-93130DEB56E5}" name="3" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{02EDDD9E-7839-4A7F-A198-B7C3BD4FE96D}" name="4" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{56C5BB89-7633-470D-BB51-9ACE7B10F91E}" name="5" dataDxfId="51"/>
+    <tableColumn id="4" xr3:uid="{CA94D498-A6BE-4017-9DCC-7DF63637F600}" name="6" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{BAD28F7F-2304-4D9A-A96E-925E4D7A8720}" name="7" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8BF43CDD-FF0D-4B54-BB5F-EC4836BC4FBD}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" dataDxfId="14" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8BF43CDD-FF0D-4B54-BB5F-EC4836BC4FBD}" name="Table6" displayName="Table6" ref="A1:E11" totalsRowShown="0" dataDxfId="48" tableBorderDxfId="47">
   <autoFilter ref="A1:E11" xr:uid="{8BF43CDD-FF0D-4B54-BB5F-EC4836BC4FBD}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{564CCDCE-84AD-44D7-AACC-6A9EED382354}" name="3" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{A3B5E53B-8CF6-46D2-BEEA-DC8C70891D0D}" name="4" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{0F227F8E-59E5-4BC0-BF12-12AB9A5FA6B0}" name="5" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{2105EB0A-1BF4-4CE9-9EFC-9F2B0E951704}" name="6" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{3EA255A5-1296-454E-A00C-C6FD41DB0182}" name="7" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{564CCDCE-84AD-44D7-AACC-6A9EED382354}" name="3" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{A3B5E53B-8CF6-46D2-BEEA-DC8C70891D0D}" name="4" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{0F227F8E-59E5-4BC0-BF12-12AB9A5FA6B0}" name="5" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{2105EB0A-1BF4-4CE9-9EFC-9F2B0E951704}" name="6" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{3EA255A5-1296-454E-A00C-C6FD41DB0182}" name="7" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{800778BD-2D99-411C-886D-C636D22BDD62}" name="Table7" displayName="Table7" ref="A1:E11" totalsRowShown="0" dataDxfId="7" tableBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{800778BD-2D99-411C-886D-C636D22BDD62}" name="Table7" displayName="Table7" ref="A1:E11" totalsRowShown="0" dataDxfId="41" tableBorderDxfId="40">
   <autoFilter ref="A1:E11" xr:uid="{800778BD-2D99-411C-886D-C636D22BDD62}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AD92C27B-2542-4A52-BD82-3B5CF67F7404}" name="3" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{D8539E53-CBDB-4479-BD7F-1E795DD35BCF}" name="4" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{5C9D68A6-4573-4972-9E46-6101950878B8}" name="5" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{FB036EA0-A0C8-4D80-AC4B-91302592EEE6}" name="6" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{F28BFB7F-7036-466F-85C7-5FDEBC770AF2}" name="7" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{AD92C27B-2542-4A52-BD82-3B5CF67F7404}" name="3" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{D8539E53-CBDB-4479-BD7F-1E795DD35BCF}" name="4" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{5C9D68A6-4573-4972-9E46-6101950878B8}" name="5" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{FB036EA0-A0C8-4D80-AC4B-91302592EEE6}" name="6" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{F28BFB7F-7036-466F-85C7-5FDEBC770AF2}" name="7" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3C065B05-5B6A-4F49-9812-13E37AF9C2EC}" name="Table8" displayName="Table8" ref="A1:E11" totalsRowShown="0" dataDxfId="0" tableBorderDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3C065B05-5B6A-4F49-9812-13E37AF9C2EC}" name="Table8" displayName="Table8" ref="A1:E11" totalsRowShown="0" dataDxfId="34" tableBorderDxfId="33">
   <autoFilter ref="A1:E11" xr:uid="{3C065B05-5B6A-4F49-9812-13E37AF9C2EC}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C6808131-FF89-4DE1-90B1-73B1E0B41F2A}" name="3" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{6C08622B-B313-49FF-8E11-5EE8FE92974E}" name="4" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{8161CC18-5A1C-4BE4-9F39-E310457946A4}" name="5" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{5D750266-1B8C-41BA-B96D-260535E2EE7F}" name="6" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{C3809118-E2EC-4DD5-B797-9A14C8AFC7E1}" name="7" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{C6808131-FF89-4DE1-90B1-73B1E0B41F2A}" name="3" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{6C08622B-B313-49FF-8E11-5EE8FE92974E}" name="4" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{8161CC18-5A1C-4BE4-9F39-E310457946A4}" name="5" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{5D750266-1B8C-41BA-B96D-260535E2EE7F}" name="6" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{C3809118-E2EC-4DD5-B797-9A14C8AFC7E1}" name="7" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{ABFE9024-074D-4473-A37A-3435575963F3}" name="Table110" displayName="Table110" ref="A1:F51" totalsRowShown="0">
+  <autoFilter ref="A1:F51" xr:uid="{ABFE9024-074D-4473-A37A-3435575963F3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F51">
+    <sortCondition ref="B1:B51"/>
+  </sortState>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{E047B987-CEA8-4E3D-B947-4FA3F51BC487}" name="experiment"/>
+    <tableColumn id="28" xr3:uid="{E3D3DEC2-6606-450F-93D1-6B535B4CB31B}" name="grado"/>
+    <tableColumn id="14" xr3:uid="{AB3A7D17-5A70-4BFF-B510-C523C5CB65FD}" name="duration_greedy"/>
+    <tableColumn id="19" xr3:uid="{4534102E-3D14-46A8-B75C-E67971494684}" name="time_taken k=1"/>
+    <tableColumn id="22" xr3:uid="{F552727C-CF71-4B21-8989-1F9DD8A80254}" name="time_taken k=2"/>
+    <tableColumn id="25" xr3:uid="{5A8B76E9-9490-404E-9CFD-3F769F2E4E50}" name="time_taken k=3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7051,20 +7845,1857 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
-        <v>0</v>
-      </c>
-      <c r="B11" s="9">
+      <c r="A11" s="8">
+        <v>0</v>
+      </c>
+      <c r="B11" s="8">
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="C11" s="9">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="E11" s="9">
-        <v>0</v>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDFD5F68-0665-4ABC-ABE7-F25883CE5CC2}">
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>5.8391094207763602E-3</v>
+      </c>
+      <c r="D2">
+        <v>0.32947918400009202</v>
+      </c>
+      <c r="E2">
+        <v>3.94191441800012</v>
+      </c>
+      <c r="F2">
+        <v>11.0907991600033</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>4.7655105590820304E-3</v>
+      </c>
+      <c r="D3">
+        <v>0.397073467999916</v>
+      </c>
+      <c r="E3">
+        <v>5.6322055990003701</v>
+      </c>
+      <c r="F3">
+        <v>9.9376720649997807</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5.6414604187011701E-3</v>
+      </c>
+      <c r="D4">
+        <v>0.37904542099999999</v>
+      </c>
+      <c r="E4">
+        <v>1.0835867760006199</v>
+      </c>
+      <c r="F4">
+        <v>2.2588137320017201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5.5739879608154297E-3</v>
+      </c>
+      <c r="D5">
+        <v>0.38748146400007499</v>
+      </c>
+      <c r="E5">
+        <v>1.6170077950000601</v>
+      </c>
+      <c r="F5">
+        <v>1.7681996000028399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>5.0759315490722604E-3</v>
+      </c>
+      <c r="D6">
+        <v>0.67830245599998296</v>
+      </c>
+      <c r="E6">
+        <v>2.4201189159994101</v>
+      </c>
+      <c r="F6">
+        <v>2.6625565289978099</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>4.7135353088378898E-3</v>
+      </c>
+      <c r="D7">
+        <v>1.0738597339998199</v>
+      </c>
+      <c r="E7">
+        <v>6.2291824710000503</v>
+      </c>
+      <c r="F7">
+        <v>12.4987078349986</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>5.3551197052001901E-3</v>
+      </c>
+      <c r="D8">
+        <v>0.50045927700011805</v>
+      </c>
+      <c r="E8">
+        <v>3.9423302899995099</v>
+      </c>
+      <c r="F8">
+        <v>7.0397920709983701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>4.8964023590087804E-3</v>
+      </c>
+      <c r="D9">
+        <v>0.46128966400010502</v>
+      </c>
+      <c r="E9">
+        <v>0.94218033300057802</v>
+      </c>
+      <c r="F9">
+        <v>1.2337920039972201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>4.8739910125732396E-3</v>
+      </c>
+      <c r="D10">
+        <v>0.51131992400019</v>
+      </c>
+      <c r="E10">
+        <v>3.0247513859994699</v>
+      </c>
+      <c r="F10">
+        <v>5.0250078690005404</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>5.3925514221191398E-3</v>
+      </c>
+      <c r="D11">
+        <v>0.40904918099999998</v>
+      </c>
+      <c r="E11">
+        <v>3.70733217999986</v>
+      </c>
+      <c r="F11">
+        <v>5.2614428929991801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>4.2402744293212804E-3</v>
+      </c>
+      <c r="D12">
+        <v>0.32831750099990098</v>
+      </c>
+      <c r="E12">
+        <v>1.97612930499963</v>
+      </c>
+      <c r="F12">
+        <v>4.5531806290018704</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>5.2533149719238203E-3</v>
+      </c>
+      <c r="D13">
+        <v>1.02013908899994</v>
+      </c>
+      <c r="E13">
+        <v>4.0276134400000903</v>
+      </c>
+      <c r="F13">
+        <v>7.4973292999966299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>4.5175552368164002E-3</v>
+      </c>
+      <c r="D14">
+        <v>0.51476440700002901</v>
+      </c>
+      <c r="E14">
+        <v>2.3248380449995198</v>
+      </c>
+      <c r="F14">
+        <v>3.1050497120013398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <v>5.1207542419433498E-3</v>
+      </c>
+      <c r="D15">
+        <v>0.40604395299988</v>
+      </c>
+      <c r="E15">
+        <v>3.6978838609993501</v>
+      </c>
+      <c r="F15">
+        <v>14.4546965439985</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>5.2807331085205E-3</v>
+      </c>
+      <c r="D16">
+        <v>0.55543062200013005</v>
+      </c>
+      <c r="E16">
+        <v>4.3720036019994897</v>
+      </c>
+      <c r="F16">
+        <v>7.4649007279986099</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>5.1751136779785104E-3</v>
+      </c>
+      <c r="D17">
+        <v>0.30605519800019398</v>
+      </c>
+      <c r="E17">
+        <v>1.6701909319999599</v>
+      </c>
+      <c r="F17">
+        <v>1.8437965720004199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>6.5302848815917899E-3</v>
+      </c>
+      <c r="D18">
+        <v>0.49575486699995902</v>
+      </c>
+      <c r="E18">
+        <v>2.9234940050000602</v>
+      </c>
+      <c r="F18">
+        <v>9.9828756200004101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>5.2385330200195304E-3</v>
+      </c>
+      <c r="D19">
+        <v>0.69679235900002801</v>
+      </c>
+      <c r="E19">
+        <v>4.3831602350001004</v>
+      </c>
+      <c r="F19">
+        <v>8.7464961510013293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>4.3635368347167899E-3</v>
+      </c>
+      <c r="D20">
+        <v>0.92259901499983199</v>
+      </c>
+      <c r="E20">
+        <v>5.2234213649999202</v>
+      </c>
+      <c r="F20">
+        <v>9.2410724220026097</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>4.8832893371581997E-3</v>
+      </c>
+      <c r="D21">
+        <v>0.26128399100002703</v>
+      </c>
+      <c r="E21">
+        <v>1.42399396600012</v>
+      </c>
+      <c r="F21">
+        <v>1.6976262800017099</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <v>4.4388771057128898E-3</v>
+      </c>
+      <c r="D22">
+        <v>0.26452542099991599</v>
+      </c>
+      <c r="E22">
+        <v>1.0734945450003499</v>
+      </c>
+      <c r="F22">
+        <v>1.3942296439999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>5.1634311676025304E-3</v>
+      </c>
+      <c r="D23">
+        <v>0.53209869900001605</v>
+      </c>
+      <c r="E23">
+        <v>5.4311040780003097</v>
+      </c>
+      <c r="F23">
+        <v>21.947997172999699</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
+        <v>5.1820278167724601E-3</v>
+      </c>
+      <c r="D24">
+        <v>0.66322177799997895</v>
+      </c>
+      <c r="E24">
+        <v>6.8767605580005604</v>
+      </c>
+      <c r="F24">
+        <v>22.323707160001501</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>5.7320594787597604E-3</v>
+      </c>
+      <c r="D25">
+        <v>0.33728040300002199</v>
+      </c>
+      <c r="E25">
+        <v>3.40073298700008</v>
+      </c>
+      <c r="F25">
+        <v>4.4836588859980102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>4.5621395111083898E-3</v>
+      </c>
+      <c r="D26">
+        <v>0.24927780999996599</v>
+      </c>
+      <c r="E26">
+        <v>2.27347767099945</v>
+      </c>
+      <c r="F26">
+        <v>2.548224811002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27">
+        <v>6.0391426086425703E-3</v>
+      </c>
+      <c r="D27">
+        <v>0.58409128599987503</v>
+      </c>
+      <c r="E27">
+        <v>3.71118901799945</v>
+      </c>
+      <c r="F27">
+        <v>10.283400188</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <v>5.4810047149658203E-3</v>
+      </c>
+      <c r="D28">
+        <v>0.35413694700014198</v>
+      </c>
+      <c r="E28">
+        <v>3.4202232380002799</v>
+      </c>
+      <c r="F28">
+        <v>9.12444181300088</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <v>4.8899650573730399E-3</v>
+      </c>
+      <c r="D29">
+        <v>0.35580247699999701</v>
+      </c>
+      <c r="E29">
+        <v>1.3709802590001301</v>
+      </c>
+      <c r="F29">
+        <v>1.47012566800185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30">
+        <v>5.0079822540283203E-3</v>
+      </c>
+      <c r="D30">
+        <v>0.21797263500002301</v>
+      </c>
+      <c r="E30">
+        <v>0.76583844600008799</v>
+      </c>
+      <c r="F30">
+        <v>0.76324663400009696</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>4.7945976257324201E-3</v>
+      </c>
+      <c r="D31">
+        <v>0.33322170599990297</v>
+      </c>
+      <c r="E31">
+        <v>3.0836209959998002</v>
+      </c>
+      <c r="F31">
+        <v>5.09110279099695</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>6.1647891998290998E-3</v>
+      </c>
+      <c r="D32">
+        <v>0.64120495799988897</v>
+      </c>
+      <c r="E32">
+        <v>6.6015620719999699</v>
+      </c>
+      <c r="F32">
+        <v>33.661860989999603</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>6.0026645660400304E-3</v>
+      </c>
+      <c r="D33">
+        <v>0.50681856599999198</v>
+      </c>
+      <c r="E33">
+        <v>2.4093096120004698</v>
+      </c>
+      <c r="F33">
+        <v>2.7303854409983601</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <v>5.6214332580566398E-3</v>
+      </c>
+      <c r="D34">
+        <v>0.21668813099995499</v>
+      </c>
+      <c r="E34">
+        <v>2.0034395640004701</v>
+      </c>
+      <c r="F34">
+        <v>2.3845861139998301</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>5.6524276733398403E-3</v>
+      </c>
+      <c r="D35">
+        <v>0.24679671700005201</v>
+      </c>
+      <c r="E35">
+        <v>3.77508114100055</v>
+      </c>
+      <c r="F35">
+        <v>6.1460980370029503</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>5.1372051239013602E-3</v>
+      </c>
+      <c r="D36">
+        <v>0.27837685899998998</v>
+      </c>
+      <c r="E36">
+        <v>1.17122840199954</v>
+      </c>
+      <c r="F36">
+        <v>1.5252734030000199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>4.7066211700439401E-3</v>
+      </c>
+      <c r="D37">
+        <v>0.21965419499997499</v>
+      </c>
+      <c r="E37">
+        <v>0.29924160400059902</v>
+      </c>
+      <c r="F37">
+        <v>0.344867935000365</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>6.2503814697265599E-3</v>
+      </c>
+      <c r="D38">
+        <v>0.43915323800001699</v>
+      </c>
+      <c r="E38">
+        <v>2.6677951359997598</v>
+      </c>
+      <c r="F38">
+        <v>3.22594257299715</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>5.1782131195068299E-3</v>
+      </c>
+      <c r="D39">
+        <v>0.26292130699994198</v>
+      </c>
+      <c r="E39">
+        <v>1.5493834219996601</v>
+      </c>
+      <c r="F39">
+        <v>2.2965890949999399</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>6.1039924621581997E-3</v>
+      </c>
+      <c r="D40">
+        <v>0.257221596999897</v>
+      </c>
+      <c r="E40">
+        <v>1.7992942900000299</v>
+      </c>
+      <c r="F40">
+        <v>2.2100352369998202</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>5.1181316375732396E-3</v>
+      </c>
+      <c r="D41">
+        <v>0.23861552500011299</v>
+      </c>
+      <c r="E41">
+        <v>3.0757520170000099</v>
+      </c>
+      <c r="F41">
+        <v>11.4139641930014</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>5.31005859375E-3</v>
+      </c>
+      <c r="D42">
+        <v>0.35698768399993203</v>
+      </c>
+      <c r="E42">
+        <v>2.90378133400008</v>
+      </c>
+      <c r="F42">
+        <v>5.6154071470009503</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>5.4419040679931597E-3</v>
+      </c>
+      <c r="D43">
+        <v>0.33055286099988701</v>
+      </c>
+      <c r="E43">
+        <v>2.1577737999996298</v>
+      </c>
+      <c r="F43">
+        <v>11.4665534910018</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>5.6045055389404297E-3</v>
+      </c>
+      <c r="D44">
+        <v>0.46214166499998999</v>
+      </c>
+      <c r="E44">
+        <v>2.6963133250001099</v>
+      </c>
+      <c r="F44">
+        <v>4.5286956169984398</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>4.8720836639404297E-3</v>
+      </c>
+      <c r="D45">
+        <v>0.289557128000069</v>
+      </c>
+      <c r="E45">
+        <v>2.0520706749994102</v>
+      </c>
+      <c r="F45">
+        <v>5.5421878640008799</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>5.0356388092040998E-3</v>
+      </c>
+      <c r="D46">
+        <v>0.35976657499986597</v>
+      </c>
+      <c r="E46">
+        <v>1.54041738000069</v>
+      </c>
+      <c r="F46">
+        <v>2.0986153119993101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>5.8310031890869097E-3</v>
+      </c>
+      <c r="D47">
+        <v>0.377706815999999</v>
+      </c>
+      <c r="E47">
+        <v>4.7512340269995503</v>
+      </c>
+      <c r="F47">
+        <v>14.7158929110009</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>5.4316520690917899E-3</v>
+      </c>
+      <c r="D48">
+        <v>0.35608616999979797</v>
+      </c>
+      <c r="E48">
+        <v>1.55985509200036</v>
+      </c>
+      <c r="F48">
+        <v>4.1092324909986901</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>4.7314167022705E-3</v>
+      </c>
+      <c r="D49">
+        <v>0.34803474099999199</v>
+      </c>
+      <c r="E49">
+        <v>1.4282287449996101</v>
+      </c>
+      <c r="F49">
+        <v>2.3426600800012198</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>4.53543663024902E-3</v>
+      </c>
+      <c r="D50">
+        <v>0.26112656500004</v>
+      </c>
+      <c r="E50">
+        <v>1.2114305909999501</v>
+      </c>
+      <c r="F50">
+        <v>3.0090908170022801</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>4.9333572387695304E-3</v>
+      </c>
+      <c r="D51">
+        <v>0.19198067499996699</v>
+      </c>
+      <c r="E51">
+        <v>1.0493775380000401</v>
+      </c>
+      <c r="F51">
+        <v>1.27878317900103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E893ECBE-0C45-4195-8C27-9C57EABA719A}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>5.8391094207763602E-3</v>
+      </c>
+      <c r="B2" s="11">
+        <v>4.2402744293212804E-3</v>
+      </c>
+      <c r="C2" s="11">
+        <v>4.4388771057128898E-3</v>
+      </c>
+      <c r="D2" s="11">
+        <v>6.1647891998290998E-3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>5.31005859375E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>4.7655105590820304E-3</v>
+      </c>
+      <c r="B3" s="9">
+        <v>5.2533149719238203E-3</v>
+      </c>
+      <c r="C3" s="9">
+        <v>5.1634311676025304E-3</v>
+      </c>
+      <c r="D3" s="9">
+        <v>6.0026645660400304E-3</v>
+      </c>
+      <c r="E3" s="9">
+        <v>5.4419040679931597E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>5.6414604187011701E-3</v>
+      </c>
+      <c r="B4" s="11">
+        <v>4.5175552368164002E-3</v>
+      </c>
+      <c r="C4" s="11">
+        <v>5.1820278167724601E-3</v>
+      </c>
+      <c r="D4" s="11">
+        <v>5.6214332580566398E-3</v>
+      </c>
+      <c r="E4" s="11">
+        <v>5.6045055389404297E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>5.5739879608154297E-3</v>
+      </c>
+      <c r="B5" s="9">
+        <v>5.1207542419433498E-3</v>
+      </c>
+      <c r="C5" s="9">
+        <v>5.7320594787597604E-3</v>
+      </c>
+      <c r="D5" s="9">
+        <v>5.6524276733398403E-3</v>
+      </c>
+      <c r="E5" s="9">
+        <v>4.8720836639404297E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>5.0759315490722604E-3</v>
+      </c>
+      <c r="B6" s="11">
+        <v>5.2807331085205E-3</v>
+      </c>
+      <c r="C6" s="11">
+        <v>4.5621395111083898E-3</v>
+      </c>
+      <c r="D6" s="11">
+        <v>5.1372051239013602E-3</v>
+      </c>
+      <c r="E6" s="11">
+        <v>5.0356388092040998E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>4.7135353088378898E-3</v>
+      </c>
+      <c r="B7" s="9">
+        <v>5.1751136779785104E-3</v>
+      </c>
+      <c r="C7" s="9">
+        <v>6.0391426086425703E-3</v>
+      </c>
+      <c r="D7" s="9">
+        <v>4.7066211700439401E-3</v>
+      </c>
+      <c r="E7" s="9">
+        <v>5.8310031890869097E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>5.3551197052001901E-3</v>
+      </c>
+      <c r="B8" s="11">
+        <v>6.5302848815917899E-3</v>
+      </c>
+      <c r="C8" s="11">
+        <v>5.4810047149658203E-3</v>
+      </c>
+      <c r="D8" s="11">
+        <v>6.2503814697265599E-3</v>
+      </c>
+      <c r="E8" s="11">
+        <v>5.4316520690917899E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>4.8964023590087804E-3</v>
+      </c>
+      <c r="B9" s="9">
+        <v>5.2385330200195304E-3</v>
+      </c>
+      <c r="C9" s="9">
+        <v>4.8899650573730399E-3</v>
+      </c>
+      <c r="D9" s="9">
+        <v>5.1782131195068299E-3</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4.7314167022705E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>4.8739910125732396E-3</v>
+      </c>
+      <c r="B10" s="11">
+        <v>4.3635368347167899E-3</v>
+      </c>
+      <c r="C10" s="11">
+        <v>5.0079822540283203E-3</v>
+      </c>
+      <c r="D10" s="11">
+        <v>6.1039924621581997E-3</v>
+      </c>
+      <c r="E10" s="11">
+        <v>4.53543663024902E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>5.3925514221191398E-3</v>
+      </c>
+      <c r="B11" s="13">
+        <v>4.8832893371581997E-3</v>
+      </c>
+      <c r="C11" s="13">
+        <v>4.7945976257324201E-3</v>
+      </c>
+      <c r="D11" s="13">
+        <v>5.1181316375732396E-3</v>
+      </c>
+      <c r="E11" s="13">
+        <v>4.9333572387695304E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D367506-84C9-41D9-B60B-328C4BC09FB0}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>0.32947918400009202</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0.32831750099990098</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.26452542099991599</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0.64120495799988897</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.35698768399993203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>0.397073467999916</v>
+      </c>
+      <c r="B3" s="9">
+        <v>1.02013908899994</v>
+      </c>
+      <c r="C3" s="9">
+        <v>0.53209869900001605</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.50681856599999198</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0.33055286099988701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>0.37904542099999999</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0.51476440700002901</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.66322177799997895</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.21668813099995499</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0.46214166499998999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>0.38748146400007499</v>
+      </c>
+      <c r="B5" s="9">
+        <v>0.40604395299988</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.33728040300002199</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.24679671700005201</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.289557128000069</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>0.67830245599998296</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0.55543062200013005</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.24927780999996599</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.27837685899998998</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0.35976657499986597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>1.0738597339998199</v>
+      </c>
+      <c r="B7" s="9">
+        <v>0.30605519800019398</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0.58409128599987503</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.21965419499997499</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.377706815999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>0.50045927700011805</v>
+      </c>
+      <c r="B8" s="11">
+        <v>0.49575486699995902</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.35413694700014198</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0.43915323800001699</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0.35608616999979797</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>0.46128966400010502</v>
+      </c>
+      <c r="B9" s="9">
+        <v>0.69679235900002801</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.35580247699999701</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0.26292130699994198</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.34803474099999199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>0.51131992400019</v>
+      </c>
+      <c r="B10" s="11">
+        <v>0.92259901499983199</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.21797263500002301</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.257221596999897</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0.26112656500004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>0.40904918099999998</v>
+      </c>
+      <c r="B11" s="13">
+        <v>0.26128399100002703</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0.33322170599990297</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0.23861552500011299</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0.19198067499996699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81613BFC-338A-4340-BF8E-055217BD48E2}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>3.94191441800012</v>
+      </c>
+      <c r="B2" s="11">
+        <v>1.97612930499963</v>
+      </c>
+      <c r="C2" s="11">
+        <v>1.0734945450003499</v>
+      </c>
+      <c r="D2" s="11">
+        <v>6.6015620719999699</v>
+      </c>
+      <c r="E2" s="11">
+        <v>2.90378133400008</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>5.6322055990003701</v>
+      </c>
+      <c r="B3" s="9">
+        <v>4.0276134400000903</v>
+      </c>
+      <c r="C3" s="9">
+        <v>5.4311040780003097</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2.4093096120004698</v>
+      </c>
+      <c r="E3" s="9">
+        <v>2.1577737999996298</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>1.0835867760006199</v>
+      </c>
+      <c r="B4" s="11">
+        <v>2.3248380449995198</v>
+      </c>
+      <c r="C4" s="11">
+        <v>6.8767605580005604</v>
+      </c>
+      <c r="D4" s="11">
+        <v>2.0034395640004701</v>
+      </c>
+      <c r="E4" s="11">
+        <v>2.6963133250001099</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>1.6170077950000601</v>
+      </c>
+      <c r="B5" s="9">
+        <v>3.6978838609993501</v>
+      </c>
+      <c r="C5" s="9">
+        <v>3.40073298700008</v>
+      </c>
+      <c r="D5" s="9">
+        <v>3.77508114100055</v>
+      </c>
+      <c r="E5" s="9">
+        <v>2.0520706749994102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>2.4201189159994101</v>
+      </c>
+      <c r="B6" s="11">
+        <v>4.3720036019994897</v>
+      </c>
+      <c r="C6" s="11">
+        <v>2.27347767099945</v>
+      </c>
+      <c r="D6" s="11">
+        <v>1.17122840199954</v>
+      </c>
+      <c r="E6" s="11">
+        <v>1.54041738000069</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>6.2291824710000503</v>
+      </c>
+      <c r="B7" s="9">
+        <v>1.6701909319999599</v>
+      </c>
+      <c r="C7" s="9">
+        <v>3.71118901799945</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.29924160400059902</v>
+      </c>
+      <c r="E7" s="9">
+        <v>4.7512340269995503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>3.9423302899995099</v>
+      </c>
+      <c r="B8" s="11">
+        <v>2.9234940050000602</v>
+      </c>
+      <c r="C8" s="11">
+        <v>3.4202232380002799</v>
+      </c>
+      <c r="D8" s="11">
+        <v>2.6677951359997598</v>
+      </c>
+      <c r="E8" s="11">
+        <v>1.55985509200036</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9">
+        <v>0.94218033300057802</v>
+      </c>
+      <c r="B9" s="9">
+        <v>4.3831602350001004</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1.3709802590001301</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1.5493834219996601</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1.4282287449996101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>3.0247513859994699</v>
+      </c>
+      <c r="B10" s="11">
+        <v>5.2234213649999202</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.76583844600008799</v>
+      </c>
+      <c r="D10" s="11">
+        <v>1.7992942900000299</v>
+      </c>
+      <c r="E10" s="11">
+        <v>1.2114305909999501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>3.70733217999986</v>
+      </c>
+      <c r="B11" s="13">
+        <v>1.42399396600012</v>
+      </c>
+      <c r="C11" s="13">
+        <v>3.0836209959998002</v>
+      </c>
+      <c r="D11" s="13">
+        <v>3.0757520170000099</v>
+      </c>
+      <c r="E11" s="13">
+        <v>1.0493775380000401</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E6BE12C-28C6-4AC9-ADE1-7E67DE87C55C}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>11.0907991600033</v>
+      </c>
+      <c r="B2" s="12">
+        <v>4.5531806290018704</v>
+      </c>
+      <c r="C2" s="12">
+        <v>1.3942296439999999</v>
+      </c>
+      <c r="D2" s="12">
+        <v>33.661860989999603</v>
+      </c>
+      <c r="E2" s="12">
+        <v>5.6154071470009503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10">
+        <v>9.9376720649997807</v>
+      </c>
+      <c r="B3" s="10">
+        <v>7.4973292999966299</v>
+      </c>
+      <c r="C3" s="10">
+        <v>21.947997172999699</v>
+      </c>
+      <c r="D3" s="10">
+        <v>2.7303854409983601</v>
+      </c>
+      <c r="E3" s="10">
+        <v>11.4665534910018</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>2.2588137320017201</v>
+      </c>
+      <c r="B4" s="12">
+        <v>3.1050497120013398</v>
+      </c>
+      <c r="C4" s="12">
+        <v>22.323707160001501</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2.3845861139998301</v>
+      </c>
+      <c r="E4" s="12">
+        <v>4.5286956169984398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>1.7681996000028399</v>
+      </c>
+      <c r="B5" s="10">
+        <v>14.4546965439985</v>
+      </c>
+      <c r="C5" s="10">
+        <v>4.4836588859980102</v>
+      </c>
+      <c r="D5" s="10">
+        <v>6.1460980370029503</v>
+      </c>
+      <c r="E5" s="10">
+        <v>5.5421878640008799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="12">
+        <v>2.6625565289978099</v>
+      </c>
+      <c r="B6" s="12">
+        <v>7.4649007279986099</v>
+      </c>
+      <c r="C6" s="12">
+        <v>2.548224811002</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1.5252734030000199</v>
+      </c>
+      <c r="E6" s="12">
+        <v>2.0986153119993101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10">
+        <v>12.4987078349986</v>
+      </c>
+      <c r="B7" s="10">
+        <v>1.8437965720004199</v>
+      </c>
+      <c r="C7" s="10">
+        <v>10.283400188</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0.344867935000365</v>
+      </c>
+      <c r="E7" s="10">
+        <v>14.7158929110009</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="12">
+        <v>7.0397920709983701</v>
+      </c>
+      <c r="B8" s="12">
+        <v>9.9828756200004101</v>
+      </c>
+      <c r="C8" s="12">
+        <v>9.12444181300088</v>
+      </c>
+      <c r="D8" s="12">
+        <v>3.22594257299715</v>
+      </c>
+      <c r="E8" s="12">
+        <v>4.1092324909986901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>1.2337920039972201</v>
+      </c>
+      <c r="B9" s="10">
+        <v>8.7464961510013293</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1.47012566800185</v>
+      </c>
+      <c r="D9" s="10">
+        <v>2.2965890949999399</v>
+      </c>
+      <c r="E9" s="10">
+        <v>2.3426600800012198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>5.0250078690005404</v>
+      </c>
+      <c r="B10" s="12">
+        <v>9.2410724220026097</v>
+      </c>
+      <c r="C10" s="12">
+        <v>0.76324663400009696</v>
+      </c>
+      <c r="D10" s="12">
+        <v>2.2100352369998202</v>
+      </c>
+      <c r="E10" s="12">
+        <v>3.0090908170022801</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>5.2614428929991801</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1.6976262800017099</v>
+      </c>
+      <c r="C11" s="14">
+        <v>5.09110279099695</v>
+      </c>
+      <c r="D11" s="14">
+        <v>11.4139641930014</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1.27878317900103</v>
       </c>
     </row>
   </sheetData>
@@ -11316,7 +13947,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11373,7 +14004,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11430,7 +14061,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11487,7 +14118,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11544,7 +14175,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11601,7 +14232,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11658,7 +14289,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11715,7 +14346,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11772,7 +14403,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -11829,7 +14460,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11886,7 +14517,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -11943,7 +14574,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12000,7 +14631,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>-3.1086244689504478E-15</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>-3.1086244689504478E-15</v>
       </c>
@@ -12057,7 +14688,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12114,7 +14745,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12171,7 +14802,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12228,7 +14859,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12285,7 +14916,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12342,7 +14973,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12399,7 +15030,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.4482758620689655E-2</v>
       </c>
@@ -12456,7 +15087,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12513,7 +15144,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="K23" s="7">
+      <c r="K23">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12570,7 +15201,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="K24" s="7">
+      <c r="K24">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12627,7 +15258,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K25" s="7">
+      <c r="K25">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12684,7 +15315,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K26" s="7">
+      <c r="K26">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12741,7 +15372,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K27">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12798,7 +15429,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>2.7777777777777776E-2</v>
       </c>
@@ -12855,7 +15486,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -12912,7 +15543,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -12969,7 +15600,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13026,7 +15657,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K32" s="7">
+      <c r="K32">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13083,7 +15714,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K33" s="7">
+      <c r="K33">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13140,7 +15771,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="K34" s="7">
+      <c r="K34">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -13197,7 +15828,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K35" s="7">
+      <c r="K35">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13254,7 +15885,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.8461538461538464E-2</v>
       </c>
-      <c r="K36" s="7">
+      <c r="K36">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.8461538461538464E-2</v>
       </c>
@@ -13311,7 +15942,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K37" s="7">
+      <c r="K37">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13368,7 +15999,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K38" s="7">
+      <c r="K38">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13425,7 +16056,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K39" s="7">
+      <c r="K39">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13482,7 +16113,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K40" s="7">
+      <c r="K40">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13539,7 +16170,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="K41" s="7">
+      <c r="K41">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.0303030303030304E-2</v>
       </c>
@@ -13596,7 +16227,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.5714285714285712E-2</v>
       </c>
-      <c r="K42" s="7">
+      <c r="K42">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>3.5714285714285712E-2</v>
       </c>
@@ -13653,7 +16284,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>5.7142857142857141E-2</v>
       </c>
-      <c r="K43" s="7">
+      <c r="K43">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>2.8571428571428571E-2</v>
       </c>
@@ -13710,7 +16341,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K44" s="7">
+      <c r="K44">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13767,7 +16398,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K45" s="7">
+      <c r="K45">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13824,7 +16455,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K46" s="7">
+      <c r="K46">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13881,7 +16512,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K47" s="7">
+      <c r="K47">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13938,7 +16569,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K48" s="7">
+      <c r="K48">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -13995,7 +16626,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K49" s="7">
+      <c r="K49">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -14052,7 +16683,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K50" s="7">
+      <c r="K50">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -14109,7 +16740,7 @@
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=2]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
-      <c r="K51" s="7">
+      <c r="K51">
         <f>(Table14[[#This Row],[optimal_iqcp]]-Table14[[#This Row],[optimal_rollout k=3]])/Table14[[#This Row],[optimal_iqcp]]</f>
         <v>0</v>
       </c>
@@ -14317,19 +16948,19 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="7">
         <v>2.7777777777777776E-2</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>6.4516129032258063E-2</v>
       </c>
     </row>
@@ -14517,19 +17148,19 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <v>0</v>
-      </c>
-      <c r="B11" s="8">
+      <c r="A11" s="7">
+        <v>0</v>
+      </c>
+      <c r="B11" s="7">
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>0</v>
       </c>
     </row>
@@ -14717,19 +17348,19 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <v>0</v>
-      </c>
-      <c r="B11" s="8">
+      <c r="A11" s="7">
+        <v>0</v>
+      </c>
+      <c r="B11" s="7">
         <v>3.4482758620689655E-2</v>
       </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
+      <c r="C11" s="7">
+        <v>0</v>
+      </c>
+      <c r="D11" s="7">
         <v>3.0303030303030304E-2</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>0</v>
       </c>
     </row>
